--- a/WpfUI/Resources/Templates/DotnetNetworking/TestCase/EnvRunNoDB.xlsx
+++ b/WpfUI/Resources/Templates/DotnetNetworking/TestCase/EnvRunNoDB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPTU\S1_SP25\CloneProject\RecordSolution_Nodejs\RecordApp\Resources\ProjectResource\DotNetWebbased\Question\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Casptone Project\Recorder_Cuong\Recorder_NetWorking\WpfUI\Resources\Templates\DotnetNetworking\TestCase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA54A6C6-D68F-4552-8232-911EA13B4703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104B9664-A63D-4B81-BA02-8DD1A8D0F466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Run" sheetId="2" r:id="rId1"/>
@@ -25,15 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Step</t>
   </si>
   <si>
     <t>Keyword action</t>
-  </si>
-  <si>
-    <t>copy_essential_files_and_folders</t>
   </si>
 </sst>
 </file>
@@ -454,14 +451,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57C292E-6388-4C7D-91A9-4D6083EF5987}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.90625" style="2"/>
+    <col min="2" max="2" width="27.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,15 +466,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
     </row>
